--- a/Excel/EDA using SQL.xlsx
+++ b/Excel/EDA using SQL.xlsx
@@ -8,19 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODES\Placements\SQL\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67C2AAA8-D7FA-4A1A-89D1-657770770D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03A4776-1F87-41C9-A828-65313BA1CEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D1DD6D53-A520-4551-8E4A-77734876DA05}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v5.0" hidden="1">Sheet1!$E$1:$E$100</definedName>
-    <definedName name="_xlchart.v5.1" hidden="1">Sheet1!$F$1:$F$100</definedName>
-    <definedName name="_xlchart.v5.2" hidden="1">Sheet1!$E$1:$E$100</definedName>
-    <definedName name="_xlchart.v5.3" hidden="1">Sheet1!$F$1:$F$100</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="30">
   <si>
     <t>Apple</t>
   </si>
@@ -118,6 +112,18 @@
   </si>
   <si>
     <t>samsung</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>std</t>
   </si>
 </sst>
 </file>
@@ -253,6 +259,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -297,6 +308,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -316,6 +332,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -335,6 +356,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -354,6 +380,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -375,6 +406,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -396,6 +432,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -417,6 +458,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -438,6 +484,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -459,6 +510,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -480,6 +536,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -502,6 +563,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -524,6 +590,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -546,6 +617,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -568,6 +644,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -590,6 +671,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -612,6 +698,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
@@ -633,6 +724,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-A782-4B72-B01D-F7B8BA48EBD5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3144,7 +3240,7 @@
                 <c:order val="20"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$22</c15:sqref>
@@ -3170,7 +3266,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3190,7 +3286,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$22:$K$22</c15:sqref>
@@ -3203,7 +3299,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000014-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3216,7 +3312,7 @@
                 <c:order val="21"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$23</c15:sqref>
@@ -3242,7 +3338,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3262,7 +3358,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$23:$K$23</c15:sqref>
@@ -3275,7 +3371,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000015-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3288,7 +3384,7 @@
                 <c:order val="22"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$24</c15:sqref>
@@ -3314,7 +3410,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3334,7 +3430,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$24:$K$24</c15:sqref>
@@ -3347,7 +3443,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000016-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3360,7 +3456,7 @@
                 <c:order val="23"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$25</c15:sqref>
@@ -3386,7 +3482,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3406,7 +3502,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$25:$K$25</c15:sqref>
@@ -3419,7 +3515,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000017-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3432,7 +3528,7 @@
                 <c:order val="24"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$26</c15:sqref>
@@ -3459,7 +3555,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3479,7 +3575,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$26:$K$26</c15:sqref>
@@ -3492,7 +3588,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000018-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3505,7 +3601,7 @@
                 <c:order val="25"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$27</c15:sqref>
@@ -3532,7 +3628,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3552,7 +3648,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$27:$K$27</c15:sqref>
@@ -3565,7 +3661,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000019-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3578,7 +3674,7 @@
                 <c:order val="26"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$28</c15:sqref>
@@ -3605,7 +3701,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3625,7 +3721,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$28:$K$28</c15:sqref>
@@ -3638,7 +3734,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001A-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3651,7 +3747,7 @@
                 <c:order val="27"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$29</c15:sqref>
@@ -3678,7 +3774,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3698,7 +3794,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$29:$K$29</c15:sqref>
@@ -3711,7 +3807,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001B-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3724,7 +3820,7 @@
                 <c:order val="28"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$30</c15:sqref>
@@ -3751,7 +3847,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3771,7 +3867,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$30:$K$30</c15:sqref>
@@ -3784,7 +3880,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001C-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3797,7 +3893,7 @@
                 <c:order val="29"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$31</c15:sqref>
@@ -3824,7 +3920,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3844,7 +3940,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$31:$K$31</c15:sqref>
@@ -3857,7 +3953,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001D-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3870,7 +3966,7 @@
                 <c:order val="30"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$32</c15:sqref>
@@ -3896,7 +3992,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3916,7 +4012,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$32:$K$32</c15:sqref>
@@ -3929,7 +4025,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001E-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -3942,7 +4038,7 @@
                 <c:order val="31"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$33</c15:sqref>
@@ -3968,7 +4064,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -3988,7 +4084,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$33:$K$33</c15:sqref>
@@ -4001,7 +4097,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001F-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4014,7 +4110,7 @@
                 <c:order val="32"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$34</c15:sqref>
@@ -4040,7 +4136,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4060,7 +4156,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$34:$K$34</c15:sqref>
@@ -4073,7 +4169,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000020-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4086,7 +4182,7 @@
                 <c:order val="33"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$35</c15:sqref>
@@ -4112,7 +4208,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4132,7 +4228,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$35:$K$35</c15:sqref>
@@ -4145,7 +4241,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000021-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4158,7 +4254,7 @@
                 <c:order val="34"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$36</c15:sqref>
@@ -4184,7 +4280,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4204,7 +4300,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$36:$K$36</c15:sqref>
@@ -4217,7 +4313,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000022-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4230,7 +4326,7 @@
                 <c:order val="35"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$37</c15:sqref>
@@ -4256,7 +4352,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4276,7 +4372,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$37:$K$37</c15:sqref>
@@ -4289,7 +4385,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000023-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4302,7 +4398,7 @@
                 <c:order val="36"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$38</c15:sqref>
@@ -4329,7 +4425,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4349,7 +4445,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$38:$K$38</c15:sqref>
@@ -4362,7 +4458,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000024-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4375,7 +4471,7 @@
                 <c:order val="37"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$39</c15:sqref>
@@ -4402,7 +4498,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4422,7 +4518,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$39:$K$39</c15:sqref>
@@ -4435,7 +4531,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000025-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4448,7 +4544,7 @@
                 <c:order val="38"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$40</c15:sqref>
@@ -4475,7 +4571,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4495,7 +4591,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$40:$K$40</c15:sqref>
@@ -4508,7 +4604,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000026-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4521,7 +4617,7 @@
                 <c:order val="39"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$41</c15:sqref>
@@ -4548,7 +4644,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4568,7 +4664,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$41:$K$41</c15:sqref>
@@ -4581,7 +4677,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000027-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4594,7 +4690,7 @@
                 <c:order val="40"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$42</c15:sqref>
@@ -4621,7 +4717,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4641,7 +4737,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$42:$K$42</c15:sqref>
@@ -4654,7 +4750,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000028-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4667,7 +4763,7 @@
                 <c:order val="41"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$43</c15:sqref>
@@ -4694,7 +4790,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4714,7 +4810,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$43:$K$43</c15:sqref>
@@ -4727,7 +4823,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000029-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4740,7 +4836,7 @@
                 <c:order val="42"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$44</c15:sqref>
@@ -4766,7 +4862,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4786,7 +4882,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$44:$K$44</c15:sqref>
@@ -4799,7 +4895,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002A-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4812,7 +4908,7 @@
                 <c:order val="43"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$45</c15:sqref>
@@ -4838,7 +4934,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4858,7 +4954,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$45:$K$45</c15:sqref>
@@ -4871,7 +4967,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002B-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4884,7 +4980,7 @@
                 <c:order val="44"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$46</c15:sqref>
@@ -4910,7 +5006,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -4930,7 +5026,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$46:$K$46</c15:sqref>
@@ -4943,7 +5039,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002C-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -4956,7 +5052,7 @@
                 <c:order val="45"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$47</c15:sqref>
@@ -4982,7 +5078,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5002,7 +5098,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$47:$K$47</c15:sqref>
@@ -5015,7 +5111,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002D-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5028,7 +5124,7 @@
                 <c:order val="46"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$48</c15:sqref>
@@ -5054,7 +5150,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5074,7 +5170,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$48:$K$48</c15:sqref>
@@ -5087,7 +5183,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002E-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5100,7 +5196,7 @@
                 <c:order val="47"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$49</c15:sqref>
@@ -5126,7 +5222,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5146,7 +5242,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$49:$K$49</c15:sqref>
@@ -5159,7 +5255,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002F-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5172,7 +5268,7 @@
                 <c:order val="48"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$50</c15:sqref>
@@ -5199,7 +5295,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5219,7 +5315,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$50:$K$50</c15:sqref>
@@ -5232,7 +5328,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000030-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5245,7 +5341,7 @@
                 <c:order val="49"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$51</c15:sqref>
@@ -5272,7 +5368,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5292,7 +5388,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$51:$K$51</c15:sqref>
@@ -5305,7 +5401,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000031-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5318,7 +5414,7 @@
                 <c:order val="50"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$52</c15:sqref>
@@ -5345,7 +5441,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5365,7 +5461,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$52:$K$52</c15:sqref>
@@ -5378,7 +5474,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000032-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5391,7 +5487,7 @@
                 <c:order val="51"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$53</c15:sqref>
@@ -5418,7 +5514,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5438,7 +5534,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$53:$K$53</c15:sqref>
@@ -5451,7 +5547,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000033-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5464,7 +5560,7 @@
                 <c:order val="52"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$54</c15:sqref>
@@ -5491,7 +5587,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5511,7 +5607,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$54:$K$54</c15:sqref>
@@ -5524,7 +5620,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000034-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5537,7 +5633,7 @@
                 <c:order val="53"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$55</c15:sqref>
@@ -5564,7 +5660,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5584,7 +5680,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$55:$K$55</c15:sqref>
@@ -5597,7 +5693,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000035-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5610,7 +5706,7 @@
                 <c:order val="54"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$56</c15:sqref>
@@ -5634,7 +5730,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5654,7 +5750,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$56:$K$56</c15:sqref>
@@ -5667,7 +5763,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000036-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5680,7 +5776,7 @@
                 <c:order val="55"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$57</c15:sqref>
@@ -5704,7 +5800,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5724,7 +5820,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$57:$K$57</c15:sqref>
@@ -5737,7 +5833,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000037-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5750,7 +5846,7 @@
                 <c:order val="56"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$58</c15:sqref>
@@ -5774,7 +5870,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5794,7 +5890,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$58:$K$58</c15:sqref>
@@ -5807,7 +5903,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000038-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5820,7 +5916,7 @@
                 <c:order val="57"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$59</c15:sqref>
@@ -5844,7 +5940,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5864,7 +5960,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$59:$K$59</c15:sqref>
@@ -5877,7 +5973,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000039-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5890,7 +5986,7 @@
                 <c:order val="58"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$60</c15:sqref>
@@ -5914,7 +6010,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -5934,7 +6030,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$60:$K$60</c15:sqref>
@@ -5947,7 +6043,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003A-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -5960,7 +6056,7 @@
                 <c:order val="59"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$61</c15:sqref>
@@ -5984,7 +6080,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6004,7 +6100,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$61:$K$61</c15:sqref>
@@ -6017,7 +6113,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003B-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6030,7 +6126,7 @@
                 <c:order val="60"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$62</c15:sqref>
@@ -6056,7 +6152,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6076,7 +6172,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$62:$K$62</c15:sqref>
@@ -6089,7 +6185,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003C-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6102,7 +6198,7 @@
                 <c:order val="61"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$63</c15:sqref>
@@ -6128,7 +6224,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6148,7 +6244,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$63:$K$63</c15:sqref>
@@ -6161,7 +6257,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003D-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6174,7 +6270,7 @@
                 <c:order val="62"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$64</c15:sqref>
@@ -6200,7 +6296,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6220,7 +6316,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$64:$K$64</c15:sqref>
@@ -6233,7 +6329,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003E-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6246,7 +6342,7 @@
                 <c:order val="63"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$65</c15:sqref>
@@ -6272,7 +6368,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6292,7 +6388,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$65:$K$65</c15:sqref>
@@ -6305,7 +6401,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003F-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6318,7 +6414,7 @@
                 <c:order val="64"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$66</c15:sqref>
@@ -6344,7 +6440,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6364,7 +6460,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$66:$K$66</c15:sqref>
@@ -6377,7 +6473,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000040-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6390,7 +6486,7 @@
                 <c:order val="65"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$67</c15:sqref>
@@ -6416,7 +6512,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6436,7 +6532,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$67:$K$67</c15:sqref>
@@ -6449,7 +6545,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000041-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6462,7 +6558,7 @@
                 <c:order val="66"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$68</c15:sqref>
@@ -6489,7 +6585,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6509,7 +6605,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$68:$K$68</c15:sqref>
@@ -6522,7 +6618,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000042-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6535,7 +6631,7 @@
                 <c:order val="67"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$69</c15:sqref>
@@ -6562,7 +6658,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6582,7 +6678,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$69:$K$69</c15:sqref>
@@ -6595,7 +6691,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000043-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6608,7 +6704,7 @@
                 <c:order val="68"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$70</c15:sqref>
@@ -6635,7 +6731,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6655,7 +6751,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$70:$K$70</c15:sqref>
@@ -6668,7 +6764,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000044-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6681,7 +6777,7 @@
                 <c:order val="69"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$71</c15:sqref>
@@ -6708,7 +6804,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6728,7 +6824,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$71:$K$71</c15:sqref>
@@ -6741,7 +6837,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000045-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6754,7 +6850,7 @@
                 <c:order val="70"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$72</c15:sqref>
@@ -6781,7 +6877,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6801,7 +6897,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$72:$K$72</c15:sqref>
@@ -6814,7 +6910,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000046-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6827,7 +6923,7 @@
                 <c:order val="71"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$73</c15:sqref>
@@ -6854,7 +6950,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6874,7 +6970,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$73:$K$73</c15:sqref>
@@ -6887,7 +6983,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000047-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6900,7 +6996,7 @@
                 <c:order val="72"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$74</c15:sqref>
@@ -6926,7 +7022,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -6946,7 +7042,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$74:$K$74</c15:sqref>
@@ -6959,7 +7055,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000048-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -6972,7 +7068,7 @@
                 <c:order val="73"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$75</c15:sqref>
@@ -6998,7 +7094,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7018,7 +7114,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$75:$K$75</c15:sqref>
@@ -7031,7 +7127,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000049-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7044,7 +7140,7 @@
                 <c:order val="74"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$76</c15:sqref>
@@ -7070,7 +7166,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7090,7 +7186,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$76:$K$76</c15:sqref>
@@ -7103,7 +7199,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004A-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7116,7 +7212,7 @@
                 <c:order val="75"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$77</c15:sqref>
@@ -7142,7 +7238,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7162,7 +7258,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$77:$K$77</c15:sqref>
@@ -7175,7 +7271,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004B-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7188,7 +7284,7 @@
                 <c:order val="76"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$78</c15:sqref>
@@ -7214,7 +7310,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7234,7 +7330,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$78:$K$78</c15:sqref>
@@ -7247,7 +7343,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004C-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7260,7 +7356,7 @@
                 <c:order val="77"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$79</c15:sqref>
@@ -7286,7 +7382,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7306,7 +7402,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$79:$K$79</c15:sqref>
@@ -7319,7 +7415,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004D-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7332,7 +7428,7 @@
                 <c:order val="78"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$80</c15:sqref>
@@ -7359,7 +7455,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7379,7 +7475,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$80:$K$80</c15:sqref>
@@ -7392,7 +7488,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004E-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7405,7 +7501,7 @@
                 <c:order val="79"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$81</c15:sqref>
@@ -7432,7 +7528,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7452,7 +7548,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$81:$K$81</c15:sqref>
@@ -7465,7 +7561,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004F-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7478,7 +7574,7 @@
                 <c:order val="80"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$82</c15:sqref>
@@ -7505,7 +7601,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7525,7 +7621,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$82:$K$82</c15:sqref>
@@ -7538,7 +7634,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000050-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7551,7 +7647,7 @@
                 <c:order val="81"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$83</c15:sqref>
@@ -7578,7 +7674,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7598,7 +7694,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$83:$K$83</c15:sqref>
@@ -7611,7 +7707,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000051-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7624,7 +7720,7 @@
                 <c:order val="82"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$84</c15:sqref>
@@ -7651,7 +7747,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7671,7 +7767,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$84:$K$84</c15:sqref>
@@ -7684,7 +7780,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000052-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7697,7 +7793,7 @@
                 <c:order val="83"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$85</c15:sqref>
@@ -7724,7 +7820,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7744,7 +7840,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$85:$K$85</c15:sqref>
@@ -7757,7 +7853,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000053-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7770,7 +7866,7 @@
                 <c:order val="84"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$86</c15:sqref>
@@ -7796,7 +7892,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7816,7 +7912,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$86:$K$86</c15:sqref>
@@ -7829,7 +7925,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000054-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7842,7 +7938,7 @@
                 <c:order val="85"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$87</c15:sqref>
@@ -7868,7 +7964,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7888,7 +7984,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$87:$K$87</c15:sqref>
@@ -7901,7 +7997,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000055-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7914,7 +8010,7 @@
                 <c:order val="86"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$88</c15:sqref>
@@ -7940,7 +8036,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -7960,7 +8056,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$88:$K$88</c15:sqref>
@@ -7973,7 +8069,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000056-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -7986,7 +8082,7 @@
                 <c:order val="87"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$89</c15:sqref>
@@ -8012,7 +8108,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8032,7 +8128,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$89:$K$89</c15:sqref>
@@ -8045,7 +8141,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000057-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8058,7 +8154,7 @@
                 <c:order val="88"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$90</c15:sqref>
@@ -8084,7 +8180,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8104,7 +8200,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$90:$K$90</c15:sqref>
@@ -8117,7 +8213,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000058-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8130,7 +8226,7 @@
                 <c:order val="89"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$91</c15:sqref>
@@ -8156,7 +8252,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8176,7 +8272,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$91:$K$91</c15:sqref>
@@ -8189,7 +8285,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000059-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8202,7 +8298,7 @@
                 <c:order val="90"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$92</c15:sqref>
@@ -8229,7 +8325,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8249,7 +8345,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$92:$K$92</c15:sqref>
@@ -8262,7 +8358,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005A-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8275,7 +8371,7 @@
                 <c:order val="91"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$93</c15:sqref>
@@ -8302,7 +8398,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8322,7 +8418,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$93:$K$93</c15:sqref>
@@ -8335,7 +8431,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005B-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8348,7 +8444,7 @@
                 <c:order val="92"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$94</c15:sqref>
@@ -8375,7 +8471,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8395,7 +8491,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$94:$K$94</c15:sqref>
@@ -8408,7 +8504,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005C-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8421,7 +8517,7 @@
                 <c:order val="93"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$95</c15:sqref>
@@ -8448,7 +8544,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8468,7 +8564,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$95:$K$95</c15:sqref>
@@ -8481,7 +8577,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005D-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8494,7 +8590,7 @@
                 <c:order val="94"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$96</c15:sqref>
@@ -8521,7 +8617,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8541,7 +8637,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$96:$K$96</c15:sqref>
@@ -8554,7 +8650,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005E-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8567,7 +8663,7 @@
                 <c:order val="95"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$97</c15:sqref>
@@ -8594,7 +8690,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8614,7 +8710,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$97:$K$97</c15:sqref>
@@ -8627,7 +8723,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005F-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8640,7 +8736,7 @@
                 <c:order val="96"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$98</c15:sqref>
@@ -8666,7 +8762,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8686,7 +8782,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$98:$K$98</c15:sqref>
@@ -8699,7 +8795,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000060-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8712,7 +8808,7 @@
                 <c:order val="97"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$99</c15:sqref>
@@ -8738,7 +8834,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8758,7 +8854,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$99:$K$99</c15:sqref>
@@ -8771,7 +8867,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000061-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -8784,7 +8880,7 @@
                 <c:order val="98"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$100</c15:sqref>
@@ -8810,7 +8906,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$1:$K$1</c15:sqref>
@@ -8830,7 +8926,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$100:$K$100</c15:sqref>
@@ -8843,7 +8939,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000062-A720-4CCE-BF1D-7427BFA275D5}"/>
                   </c:ext>
@@ -10509,7 +10605,7 @@
                 <c:order val="20"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$22</c15:sqref>
@@ -10536,7 +10632,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -10559,7 +10655,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$22:$Q$22</c15:sqref>
@@ -10572,7 +10668,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000014-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -10585,7 +10681,7 @@
                 <c:order val="21"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$23</c15:sqref>
@@ -10612,7 +10708,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -10635,7 +10731,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$23:$Q$23</c15:sqref>
@@ -10648,7 +10744,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000015-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -10661,7 +10757,7 @@
                 <c:order val="22"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$24</c15:sqref>
@@ -10688,7 +10784,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -10711,7 +10807,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$24:$Q$24</c15:sqref>
@@ -10724,7 +10820,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000016-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -10737,7 +10833,7 @@
                 <c:order val="23"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$25</c15:sqref>
@@ -10764,7 +10860,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -10787,7 +10883,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$25:$Q$25</c15:sqref>
@@ -10800,7 +10896,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000017-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -10813,7 +10909,7 @@
                 <c:order val="24"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$26</c15:sqref>
@@ -10841,7 +10937,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -10864,7 +10960,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$26:$Q$26</c15:sqref>
@@ -10877,7 +10973,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000018-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -10890,7 +10986,7 @@
                 <c:order val="25"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$27</c15:sqref>
@@ -10918,7 +11014,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -10941,7 +11037,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$27:$Q$27</c15:sqref>
@@ -10954,7 +11050,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000019-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -10967,7 +11063,7 @@
                 <c:order val="26"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$28</c15:sqref>
@@ -10995,7 +11091,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11018,7 +11114,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$28:$Q$28</c15:sqref>
@@ -11031,7 +11127,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001A-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11044,7 +11140,7 @@
                 <c:order val="27"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$29</c15:sqref>
@@ -11072,7 +11168,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11095,7 +11191,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$29:$Q$29</c15:sqref>
@@ -11108,7 +11204,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001B-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11121,7 +11217,7 @@
                 <c:order val="28"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$30</c15:sqref>
@@ -11149,7 +11245,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11172,7 +11268,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$30:$Q$30</c15:sqref>
@@ -11185,7 +11281,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001C-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11198,7 +11294,7 @@
                 <c:order val="29"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$31</c15:sqref>
@@ -11226,7 +11322,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11249,7 +11345,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$31:$Q$31</c15:sqref>
@@ -11262,7 +11358,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001D-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11275,7 +11371,7 @@
                 <c:order val="30"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$32</c15:sqref>
@@ -11302,7 +11398,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11325,7 +11421,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$32:$Q$32</c15:sqref>
@@ -11338,7 +11434,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001E-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11351,7 +11447,7 @@
                 <c:order val="31"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$33</c15:sqref>
@@ -11378,7 +11474,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11401,7 +11497,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$33:$Q$33</c15:sqref>
@@ -11414,7 +11510,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000001F-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11427,7 +11523,7 @@
                 <c:order val="32"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$34</c15:sqref>
@@ -11454,7 +11550,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11477,7 +11573,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$34:$Q$34</c15:sqref>
@@ -11490,7 +11586,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000020-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11503,7 +11599,7 @@
                 <c:order val="33"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$35</c15:sqref>
@@ -11530,7 +11626,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11553,7 +11649,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$35:$Q$35</c15:sqref>
@@ -11566,7 +11662,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000021-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11579,7 +11675,7 @@
                 <c:order val="34"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$36</c15:sqref>
@@ -11606,7 +11702,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11629,7 +11725,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$36:$Q$36</c15:sqref>
@@ -11642,7 +11738,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000022-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11655,7 +11751,7 @@
                 <c:order val="35"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$37</c15:sqref>
@@ -11682,7 +11778,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11705,7 +11801,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$37:$Q$37</c15:sqref>
@@ -11718,7 +11814,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000023-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11731,7 +11827,7 @@
                 <c:order val="36"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$38</c15:sqref>
@@ -11759,7 +11855,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11782,7 +11878,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$38:$Q$38</c15:sqref>
@@ -11795,7 +11891,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000024-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11808,7 +11904,7 @@
                 <c:order val="37"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$39</c15:sqref>
@@ -11836,7 +11932,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11859,7 +11955,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$39:$Q$39</c15:sqref>
@@ -11872,7 +11968,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000025-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11885,7 +11981,7 @@
                 <c:order val="38"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$40</c15:sqref>
@@ -11913,7 +12009,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -11936,7 +12032,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$40:$Q$40</c15:sqref>
@@ -11949,7 +12045,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000026-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -11962,7 +12058,7 @@
                 <c:order val="39"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$41</c15:sqref>
@@ -11990,7 +12086,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12013,7 +12109,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$41:$Q$41</c15:sqref>
@@ -12026,7 +12122,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000027-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12039,7 +12135,7 @@
                 <c:order val="40"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$42</c15:sqref>
@@ -12067,7 +12163,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12090,7 +12186,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$42:$Q$42</c15:sqref>
@@ -12103,7 +12199,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000028-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12116,7 +12212,7 @@
                 <c:order val="41"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$43</c15:sqref>
@@ -12144,7 +12240,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12167,7 +12263,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$43:$Q$43</c15:sqref>
@@ -12180,7 +12276,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000029-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12193,7 +12289,7 @@
                 <c:order val="42"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$44</c15:sqref>
@@ -12220,7 +12316,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12243,7 +12339,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$44:$Q$44</c15:sqref>
@@ -12256,7 +12352,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002A-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12269,7 +12365,7 @@
                 <c:order val="43"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$45</c15:sqref>
@@ -12296,7 +12392,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12319,7 +12415,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$45:$Q$45</c15:sqref>
@@ -12332,7 +12428,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002B-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12345,7 +12441,7 @@
                 <c:order val="44"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$46</c15:sqref>
@@ -12372,7 +12468,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12395,7 +12491,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$46:$Q$46</c15:sqref>
@@ -12408,7 +12504,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002C-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12421,7 +12517,7 @@
                 <c:order val="45"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$47</c15:sqref>
@@ -12448,7 +12544,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12471,7 +12567,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$47:$Q$47</c15:sqref>
@@ -12484,7 +12580,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002D-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12497,7 +12593,7 @@
                 <c:order val="46"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$48</c15:sqref>
@@ -12524,7 +12620,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12547,7 +12643,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$48:$Q$48</c15:sqref>
@@ -12560,7 +12656,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002E-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12573,7 +12669,7 @@
                 <c:order val="47"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$49</c15:sqref>
@@ -12600,7 +12696,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12623,7 +12719,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$49:$Q$49</c15:sqref>
@@ -12636,7 +12732,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000002F-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12649,7 +12745,7 @@
                 <c:order val="48"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$50</c15:sqref>
@@ -12677,7 +12773,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12700,7 +12796,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$50:$Q$50</c15:sqref>
@@ -12713,7 +12809,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000030-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12726,7 +12822,7 @@
                 <c:order val="49"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$51</c15:sqref>
@@ -12754,7 +12850,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12777,7 +12873,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$51:$Q$51</c15:sqref>
@@ -12790,7 +12886,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000031-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12803,7 +12899,7 @@
                 <c:order val="50"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$52</c15:sqref>
@@ -12831,7 +12927,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12854,7 +12950,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$52:$Q$52</c15:sqref>
@@ -12867,7 +12963,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000032-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12880,7 +12976,7 @@
                 <c:order val="51"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$53</c15:sqref>
@@ -12908,7 +13004,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -12931,7 +13027,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$53:$Q$53</c15:sqref>
@@ -12944,7 +13040,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000033-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -12957,7 +13053,7 @@
                 <c:order val="52"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$54</c15:sqref>
@@ -12985,7 +13081,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13008,7 +13104,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$54:$Q$54</c15:sqref>
@@ -13021,7 +13117,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000034-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13034,7 +13130,7 @@
                 <c:order val="53"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$55</c15:sqref>
@@ -13062,7 +13158,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13085,7 +13181,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$55:$Q$55</c15:sqref>
@@ -13098,7 +13194,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000035-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13111,7 +13207,7 @@
                 <c:order val="54"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$56</c15:sqref>
@@ -13136,7 +13232,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13159,7 +13255,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$56:$Q$56</c15:sqref>
@@ -13172,7 +13268,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000036-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13185,7 +13281,7 @@
                 <c:order val="55"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$57</c15:sqref>
@@ -13210,7 +13306,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13233,7 +13329,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$57:$Q$57</c15:sqref>
@@ -13246,7 +13342,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000037-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13259,7 +13355,7 @@
                 <c:order val="56"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$58</c15:sqref>
@@ -13284,7 +13380,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13307,7 +13403,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$58:$Q$58</c15:sqref>
@@ -13320,7 +13416,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000038-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13333,7 +13429,7 @@
                 <c:order val="57"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$59</c15:sqref>
@@ -13358,7 +13454,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13381,7 +13477,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$59:$Q$59</c15:sqref>
@@ -13394,7 +13490,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000039-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13407,7 +13503,7 @@
                 <c:order val="58"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$60</c15:sqref>
@@ -13432,7 +13528,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13455,7 +13551,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$60:$Q$60</c15:sqref>
@@ -13468,7 +13564,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003A-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13481,7 +13577,7 @@
                 <c:order val="59"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$61</c15:sqref>
@@ -13506,7 +13602,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13529,7 +13625,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$61:$Q$61</c15:sqref>
@@ -13542,7 +13638,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003B-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13555,7 +13651,7 @@
                 <c:order val="60"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$62</c15:sqref>
@@ -13582,7 +13678,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13605,7 +13701,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$62:$Q$62</c15:sqref>
@@ -13618,7 +13714,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003C-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13631,7 +13727,7 @@
                 <c:order val="61"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$63</c15:sqref>
@@ -13658,7 +13754,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13681,7 +13777,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$63:$Q$63</c15:sqref>
@@ -13694,7 +13790,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003D-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13707,7 +13803,7 @@
                 <c:order val="62"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$64</c15:sqref>
@@ -13734,7 +13830,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13757,7 +13853,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$64:$Q$64</c15:sqref>
@@ -13770,7 +13866,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003E-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13783,7 +13879,7 @@
                 <c:order val="63"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$65</c15:sqref>
@@ -13810,7 +13906,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13833,7 +13929,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$65:$Q$65</c15:sqref>
@@ -13846,7 +13942,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000003F-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13859,7 +13955,7 @@
                 <c:order val="64"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$66</c15:sqref>
@@ -13886,7 +13982,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13909,7 +14005,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$66:$Q$66</c15:sqref>
@@ -13922,7 +14018,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000040-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -13935,7 +14031,7 @@
                 <c:order val="65"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$67</c15:sqref>
@@ -13962,7 +14058,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -13985,7 +14081,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$67:$Q$67</c15:sqref>
@@ -13998,7 +14094,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000041-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14011,7 +14107,7 @@
                 <c:order val="66"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$68</c15:sqref>
@@ -14039,7 +14135,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14062,7 +14158,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$68:$Q$68</c15:sqref>
@@ -14075,7 +14171,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000042-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14088,7 +14184,7 @@
                 <c:order val="67"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$69</c15:sqref>
@@ -14116,7 +14212,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14139,7 +14235,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$69:$Q$69</c15:sqref>
@@ -14152,7 +14248,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000043-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14165,7 +14261,7 @@
                 <c:order val="68"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$70</c15:sqref>
@@ -14193,7 +14289,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14216,7 +14312,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$70:$Q$70</c15:sqref>
@@ -14229,7 +14325,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000044-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14242,7 +14338,7 @@
                 <c:order val="69"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$71</c15:sqref>
@@ -14270,7 +14366,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14293,7 +14389,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$71:$Q$71</c15:sqref>
@@ -14306,7 +14402,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000045-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14319,7 +14415,7 @@
                 <c:order val="70"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$72</c15:sqref>
@@ -14347,7 +14443,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14370,7 +14466,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$72:$Q$72</c15:sqref>
@@ -14383,7 +14479,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000046-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14396,7 +14492,7 @@
                 <c:order val="71"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$73</c15:sqref>
@@ -14424,7 +14520,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14447,7 +14543,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$73:$Q$73</c15:sqref>
@@ -14460,7 +14556,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000047-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14473,7 +14569,7 @@
                 <c:order val="72"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$74</c15:sqref>
@@ -14500,7 +14596,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14523,7 +14619,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$74:$Q$74</c15:sqref>
@@ -14536,7 +14632,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000048-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14549,7 +14645,7 @@
                 <c:order val="73"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$75</c15:sqref>
@@ -14576,7 +14672,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14599,7 +14695,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$75:$Q$75</c15:sqref>
@@ -14612,7 +14708,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000049-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14625,7 +14721,7 @@
                 <c:order val="74"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$76</c15:sqref>
@@ -14652,7 +14748,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14675,7 +14771,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$76:$Q$76</c15:sqref>
@@ -14688,7 +14784,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004A-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14701,7 +14797,7 @@
                 <c:order val="75"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$77</c15:sqref>
@@ -14728,7 +14824,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14751,7 +14847,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$77:$Q$77</c15:sqref>
@@ -14764,7 +14860,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004B-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14777,7 +14873,7 @@
                 <c:order val="76"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$78</c15:sqref>
@@ -14804,7 +14900,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14827,7 +14923,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$78:$Q$78</c15:sqref>
@@ -14840,7 +14936,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004C-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14853,7 +14949,7 @@
                 <c:order val="77"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$79</c15:sqref>
@@ -14880,7 +14976,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14903,7 +14999,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$79:$Q$79</c15:sqref>
@@ -14916,7 +15012,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004D-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -14929,7 +15025,7 @@
                 <c:order val="78"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$80</c15:sqref>
@@ -14957,7 +15053,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -14980,7 +15076,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$80:$Q$80</c15:sqref>
@@ -14993,7 +15089,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004E-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15006,7 +15102,7 @@
                 <c:order val="79"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$81</c15:sqref>
@@ -15034,7 +15130,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15057,7 +15153,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$81:$Q$81</c15:sqref>
@@ -15070,7 +15166,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000004F-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15083,7 +15179,7 @@
                 <c:order val="80"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$82</c15:sqref>
@@ -15111,7 +15207,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15134,7 +15230,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$82:$Q$82</c15:sqref>
@@ -15147,7 +15243,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000050-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15160,7 +15256,7 @@
                 <c:order val="81"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$83</c15:sqref>
@@ -15188,7 +15284,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15211,7 +15307,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$83:$Q$83</c15:sqref>
@@ -15224,7 +15320,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000051-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15237,7 +15333,7 @@
                 <c:order val="82"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$84</c15:sqref>
@@ -15265,7 +15361,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15288,7 +15384,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$84:$Q$84</c15:sqref>
@@ -15301,7 +15397,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000052-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15314,7 +15410,7 @@
                 <c:order val="83"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$85</c15:sqref>
@@ -15342,7 +15438,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15365,7 +15461,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$85:$Q$85</c15:sqref>
@@ -15378,7 +15474,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000053-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15391,7 +15487,7 @@
                 <c:order val="84"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$86</c15:sqref>
@@ -15418,7 +15514,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15441,7 +15537,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$86:$Q$86</c15:sqref>
@@ -15454,7 +15550,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000054-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15467,7 +15563,7 @@
                 <c:order val="85"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$87</c15:sqref>
@@ -15494,7 +15590,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15517,7 +15613,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$87:$Q$87</c15:sqref>
@@ -15530,7 +15626,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000055-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15543,7 +15639,7 @@
                 <c:order val="86"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$88</c15:sqref>
@@ -15570,7 +15666,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15593,7 +15689,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$88:$Q$88</c15:sqref>
@@ -15606,7 +15702,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000056-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15619,7 +15715,7 @@
                 <c:order val="87"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$89</c15:sqref>
@@ -15646,7 +15742,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15669,7 +15765,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$89:$Q$89</c15:sqref>
@@ -15682,7 +15778,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000057-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15695,7 +15791,7 @@
                 <c:order val="88"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$90</c15:sqref>
@@ -15722,7 +15818,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15745,7 +15841,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$90:$Q$90</c15:sqref>
@@ -15758,7 +15854,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000058-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15771,7 +15867,7 @@
                 <c:order val="89"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$91</c15:sqref>
@@ -15798,7 +15894,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15821,7 +15917,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$91:$Q$91</c15:sqref>
@@ -15834,7 +15930,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000059-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15847,7 +15943,7 @@
                 <c:order val="90"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$92</c15:sqref>
@@ -15875,7 +15971,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15898,7 +15994,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$92:$Q$92</c15:sqref>
@@ -15911,7 +16007,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005A-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -15924,7 +16020,7 @@
                 <c:order val="91"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$93</c15:sqref>
@@ -15952,7 +16048,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -15975,7 +16071,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$93:$Q$93</c15:sqref>
@@ -15988,7 +16084,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005B-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16001,7 +16097,7 @@
                 <c:order val="92"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$94</c15:sqref>
@@ -16029,7 +16125,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16052,7 +16148,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$94:$Q$94</c15:sqref>
@@ -16065,7 +16161,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005C-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16078,7 +16174,7 @@
                 <c:order val="93"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$95</c15:sqref>
@@ -16106,7 +16202,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16129,7 +16225,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$95:$Q$95</c15:sqref>
@@ -16142,7 +16238,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005D-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16155,7 +16251,7 @@
                 <c:order val="94"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$96</c15:sqref>
@@ -16183,7 +16279,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16206,7 +16302,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$96:$Q$96</c15:sqref>
@@ -16219,7 +16315,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005E-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16232,7 +16328,7 @@
                 <c:order val="95"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$97</c15:sqref>
@@ -16260,7 +16356,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16283,7 +16379,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$97:$Q$97</c15:sqref>
@@ -16296,7 +16392,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000005F-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16309,7 +16405,7 @@
                 <c:order val="96"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$98</c15:sqref>
@@ -16336,7 +16432,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16359,7 +16455,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$98:$Q$98</c15:sqref>
@@ -16372,7 +16468,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000060-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16385,7 +16481,7 @@
                 <c:order val="97"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$99</c15:sqref>
@@ -16412,7 +16508,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16435,7 +16531,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$99:$Q$99</c15:sqref>
@@ -16448,7 +16544,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000061-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -16461,7 +16557,7 @@
                 <c:order val="98"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$N$100</c15:sqref>
@@ -16488,7 +16584,7 @@
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$1:$Q$1</c15:sqref>
@@ -16511,7 +16607,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$O$100:$Q$100</c15:sqref>
@@ -16524,7 +16620,7 @@
                     </c:numCache>
                   </c:numRef>
                 </c:val>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000062-9F66-49B7-BF44-95FEB37924D8}"/>
                   </c:ext>
@@ -19360,10 +19456,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93269711-1032-4E3F-A336-E2A1EC193001}">
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:W100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -19397,8 +19493,23 @@
       <c r="Q1" t="s">
         <v>25</v>
       </c>
+      <c r="S1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -19432,8 +19543,23 @@
       <c r="Q2">
         <v>0</v>
       </c>
+      <c r="S2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>47896</v>
+      </c>
+      <c r="U2">
+        <v>152274</v>
+      </c>
+      <c r="V2">
+        <v>83340.571400000001</v>
+      </c>
+      <c r="W2">
+        <v>29202.067913683299</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -19467,8 +19593,23 @@
       <c r="Q3">
         <v>0</v>
       </c>
+      <c r="S3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>11136</v>
+      </c>
+      <c r="U3">
+        <v>233846</v>
+      </c>
+      <c r="V3">
+        <v>57214.424800000001</v>
+      </c>
+      <c r="W3">
+        <v>33094.250798151697</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -19502,8 +19643,23 @@
       <c r="Q4">
         <v>0</v>
       </c>
+      <c r="S4" t="s">
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <v>9271</v>
+      </c>
+      <c r="U4">
+        <v>138475</v>
+      </c>
+      <c r="V4">
+        <v>33394.631099999999</v>
+      </c>
+      <c r="W4">
+        <v>19918.418409154401</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -19537,8 +19693,23 @@
       <c r="Q5">
         <v>0</v>
       </c>
+      <c r="S5" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>10603</v>
+      </c>
+      <c r="U5">
+        <v>211788</v>
+      </c>
+      <c r="V5">
+        <v>58972.397400000002</v>
+      </c>
+      <c r="W5">
+        <v>37286.059599499502</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -19572,8 +19743,23 @@
       <c r="Q6">
         <v>0</v>
       </c>
+      <c r="S6" t="s">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>14647</v>
+      </c>
+      <c r="U6">
+        <v>194973</v>
+      </c>
+      <c r="V6">
+        <v>63009.629399999998</v>
+      </c>
+      <c r="W6">
+        <v>35949.224385007401</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -19607,8 +19793,23 @@
       <c r="Q7">
         <v>0</v>
       </c>
+      <c r="S7" t="s">
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <v>12201</v>
+      </c>
+      <c r="U7">
+        <v>261019</v>
+      </c>
+      <c r="V7">
+        <v>58072.565499999997</v>
+      </c>
+      <c r="W7">
+        <v>36966.957485134903</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -19642,8 +19843,23 @@
       <c r="Q8">
         <v>0</v>
       </c>
+      <c r="S8" t="s">
+        <v>6</v>
+      </c>
+      <c r="T8">
+        <v>13053</v>
+      </c>
+      <c r="U8">
+        <v>23923</v>
+      </c>
+      <c r="V8">
+        <v>16745.666700000002</v>
+      </c>
+      <c r="W8">
+        <v>5075.8514118870298</v>
+      </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -19677,8 +19893,23 @@
       <c r="Q9">
         <v>0</v>
       </c>
+      <c r="S9" t="s">
+        <v>7</v>
+      </c>
+      <c r="T9">
+        <v>44702</v>
+      </c>
+      <c r="U9">
+        <v>149131</v>
+      </c>
+      <c r="V9">
+        <v>91814.603799999997</v>
+      </c>
+      <c r="W9">
+        <v>28169.901709354599</v>
+      </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -19712,8 +19943,23 @@
       <c r="Q10">
         <v>0</v>
       </c>
+      <c r="S10" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10">
+        <v>52694</v>
+      </c>
+      <c r="U10">
+        <v>137942</v>
+      </c>
+      <c r="V10">
+        <v>85903.833299999998</v>
+      </c>
+      <c r="W10">
+        <v>29106.372678027401</v>
+      </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -19747,8 +19993,23 @@
       <c r="Q11">
         <v>0</v>
       </c>
+      <c r="S11" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11">
+        <v>23816</v>
+      </c>
+      <c r="U11">
+        <v>149131</v>
+      </c>
+      <c r="V11">
+        <v>66747.383000000002</v>
+      </c>
+      <c r="W11">
+        <v>24904.707970329</v>
+      </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -19782,8 +20043,23 @@
       <c r="Q12">
         <v>0</v>
       </c>
+      <c r="S12" t="s">
+        <v>10</v>
+      </c>
+      <c r="T12">
+        <v>71875</v>
+      </c>
+      <c r="U12">
+        <v>79867</v>
+      </c>
+      <c r="V12">
+        <v>75871</v>
+      </c>
+      <c r="W12">
+        <v>3996</v>
+      </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -19817,8 +20093,23 @@
       <c r="Q13">
         <v>0</v>
       </c>
+      <c r="S13" t="s">
+        <v>11</v>
+      </c>
+      <c r="T13">
+        <v>49817</v>
+      </c>
+      <c r="U13">
+        <v>74589</v>
+      </c>
+      <c r="V13">
+        <v>60391</v>
+      </c>
+      <c r="W13">
+        <v>9698.2498421106793</v>
+      </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -19852,8 +20143,23 @@
       <c r="Q14">
         <v>0</v>
       </c>
+      <c r="S14" t="s">
+        <v>12</v>
+      </c>
+      <c r="T14">
+        <v>10443</v>
+      </c>
+      <c r="U14">
+        <v>13853</v>
+      </c>
+      <c r="V14">
+        <v>11584.5</v>
+      </c>
+      <c r="W14">
+        <v>1339.06487893604</v>
+      </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -19887,8 +20193,23 @@
       <c r="Q15">
         <v>0</v>
       </c>
+      <c r="S15" t="s">
+        <v>13</v>
+      </c>
+      <c r="T15">
+        <v>54825</v>
+      </c>
+      <c r="U15">
+        <v>324955</v>
+      </c>
+      <c r="V15">
+        <v>178282.71429999999</v>
+      </c>
+      <c r="W15">
+        <v>91749.021141861696</v>
+      </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -19922,8 +20243,23 @@
       <c r="Q16">
         <v>0</v>
       </c>
+      <c r="S16" t="s">
+        <v>14</v>
+      </c>
+      <c r="T16">
+        <v>12734</v>
+      </c>
+      <c r="U16">
+        <v>20726</v>
+      </c>
+      <c r="V16">
+        <v>15717.571400000001</v>
+      </c>
+      <c r="W16">
+        <v>2992.33968932782</v>
+      </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -19957,8 +20293,23 @@
       <c r="Q17">
         <v>1</v>
       </c>
+      <c r="S17" t="s">
+        <v>15</v>
+      </c>
+      <c r="T17">
+        <v>14332</v>
+      </c>
+      <c r="U17">
+        <v>98515</v>
+      </c>
+      <c r="V17">
+        <v>75308.555600000007</v>
+      </c>
+      <c r="W17">
+        <v>27955.1783877577</v>
+      </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -19992,8 +20343,23 @@
       <c r="Q18">
         <v>0</v>
       </c>
+      <c r="S18" t="s">
+        <v>16</v>
+      </c>
+      <c r="T18">
+        <v>67932</v>
+      </c>
+      <c r="U18">
+        <v>117163</v>
+      </c>
+      <c r="V18">
+        <v>89386.333299999998</v>
+      </c>
+      <c r="W18">
+        <v>20589.669971992102</v>
+      </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -20027,8 +20393,23 @@
       <c r="Q19">
         <v>0</v>
       </c>
+      <c r="S19" t="s">
+        <v>17</v>
+      </c>
+      <c r="T19">
+        <v>34579</v>
+      </c>
+      <c r="U19">
+        <v>42571</v>
+      </c>
+      <c r="V19">
+        <v>38575</v>
+      </c>
+      <c r="W19">
+        <v>3996</v>
+      </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -20062,8 +20443,23 @@
       <c r="Q20">
         <v>0</v>
       </c>
+      <c r="S20" t="s">
+        <v>18</v>
+      </c>
+      <c r="T20">
+        <v>101179</v>
+      </c>
+      <c r="U20">
+        <v>122491</v>
+      </c>
+      <c r="V20">
+        <v>111835</v>
+      </c>
+      <c r="W20">
+        <v>8700.5875663658408</v>
+      </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E21">
         <v>2.5</v>
       </c>
@@ -20071,7 +20467,7 @@
         <v>53227</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E22">
         <v>1.5</v>
       </c>
@@ -20079,7 +20475,7 @@
         <v>13746</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E23">
         <v>1.6</v>
       </c>
@@ -20087,7 +20483,7 @@
         <v>43636</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E24">
         <v>1.8</v>
       </c>
@@ -20095,7 +20491,7 @@
         <v>35112</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E25">
         <v>2</v>
       </c>
@@ -20103,7 +20499,7 @@
         <v>22305</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E26">
         <v>1.6</v>
       </c>
@@ -20111,7 +20507,7 @@
         <v>58555</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E27">
         <v>1.6</v>
       </c>
@@ -20119,7 +20515,7 @@
         <v>42624</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E28">
         <v>1.9</v>
       </c>
@@ -20127,7 +20523,7 @@
         <v>69157</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E29">
         <v>1.6</v>
       </c>
@@ -20135,7 +20531,7 @@
         <v>47739</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E30">
         <v>1.44</v>
       </c>
@@ -20143,7 +20539,7 @@
         <v>13053</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E31">
         <v>1.5</v>
       </c>
@@ -20151,7 +20547,7 @@
         <v>10603</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E32">
         <v>2.5</v>
       </c>
